--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/143.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/143.xlsx
@@ -426,13 +426,13 @@
         <v>-6.741914986342854</v>
       </c>
       <c r="E2">
-        <v>-9.870259495351906</v>
+        <v>-12.76382306050704</v>
       </c>
       <c r="F2">
-        <v>2.031034954408669</v>
+        <v>2.316250134866566</v>
       </c>
       <c r="G2">
-        <v>-3.962492422988196</v>
+        <v>-4.471942344390021</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-6.379751179149157</v>
       </c>
       <c r="E3">
-        <v>-12.20217454323172</v>
+        <v>-12.57779787674595</v>
       </c>
       <c r="F3">
-        <v>1.998856194279519</v>
+        <v>2.101575408961463</v>
       </c>
       <c r="G3">
-        <v>-2.684737713923392</v>
+        <v>-4.58142208537372</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-6.083091037565902</v>
       </c>
       <c r="E4">
-        <v>-10.70607994294762</v>
+        <v>-12.96971918821379</v>
       </c>
       <c r="F4">
-        <v>1.994016871912364</v>
+        <v>2.135858222293724</v>
       </c>
       <c r="G4">
-        <v>-3.113870489996959</v>
+        <v>-4.000474311960254</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-5.884717587301884</v>
       </c>
       <c r="E5">
-        <v>-11.99294545865532</v>
+        <v>-13.06303745208985</v>
       </c>
       <c r="F5">
-        <v>2.033564788456818</v>
+        <v>2.106336864792755</v>
       </c>
       <c r="G5">
-        <v>-1.870111773074931</v>
+        <v>-3.942235194833395</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-5.789211511423536</v>
       </c>
       <c r="E6">
-        <v>-11.84284465919708</v>
+        <v>-14.54898374212276</v>
       </c>
       <c r="F6">
-        <v>2.18942045855874</v>
+        <v>2.566789855843277</v>
       </c>
       <c r="G6">
-        <v>-2.085972584417569</v>
+        <v>-3.985967501407168</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-5.800648435313912</v>
       </c>
       <c r="E7">
-        <v>-11.81335523645913</v>
+        <v>-14.4163492669121</v>
       </c>
       <c r="F7">
-        <v>2.35553463057693</v>
+        <v>2.60484339759308</v>
       </c>
       <c r="G7">
-        <v>-2.549326469730583</v>
+        <v>-3.725003817637499</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-5.908357981920983</v>
       </c>
       <c r="E8">
-        <v>-13.57550674164188</v>
+        <v>-14.00439851490834</v>
       </c>
       <c r="F8">
-        <v>1.938015922013506</v>
+        <v>2.578847571758426</v>
       </c>
       <c r="G8">
-        <v>-2.777744180303677</v>
+        <v>-4.586934143696606</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-6.090667001068935</v>
       </c>
       <c r="E9">
-        <v>-13.36587009440479</v>
+        <v>-14.82615352223623</v>
       </c>
       <c r="F9">
-        <v>2.666647889515951</v>
+        <v>2.866950440982483</v>
       </c>
       <c r="G9">
-        <v>-2.849880967604396</v>
+        <v>-3.726900760231501</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-6.331533699102341</v>
       </c>
       <c r="E10">
-        <v>-15.17448827138024</v>
+        <v>-15.52454836912118</v>
       </c>
       <c r="F10">
-        <v>3.216113928201697</v>
+        <v>2.758962809618734</v>
       </c>
       <c r="G10">
-        <v>-1.056780255532325</v>
+        <v>-3.420486596753178</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-6.60736313434059</v>
       </c>
       <c r="E11">
-        <v>-14.88197149285477</v>
+        <v>-17.0465775400472</v>
       </c>
       <c r="F11">
-        <v>2.852185620394985</v>
+        <v>3.208869026896813</v>
       </c>
       <c r="G11">
-        <v>-1.621711609626796</v>
+        <v>-3.787126204681922</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-6.892023432680633</v>
       </c>
       <c r="E12">
-        <v>-13.58942274226745</v>
+        <v>-17.0515996177217</v>
       </c>
       <c r="F12">
-        <v>3.120884811575866</v>
+        <v>3.338241791131234</v>
       </c>
       <c r="G12">
-        <v>-1.681735110799322</v>
+        <v>-3.806582280816219</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-7.156318115155557</v>
       </c>
       <c r="E13">
-        <v>-15.74104565447988</v>
+        <v>-17.23358540266795</v>
       </c>
       <c r="F13">
-        <v>3.20642699979336</v>
+        <v>3.58424702894502</v>
       </c>
       <c r="G13">
-        <v>-1.472002119249874</v>
+        <v>-3.852734596179199</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-7.389049939717378</v>
       </c>
       <c r="E14">
-        <v>-15.16496941901612</v>
+        <v>-17.74739964900025</v>
       </c>
       <c r="F14">
-        <v>3.529283195034467</v>
+        <v>3.993101014475161</v>
       </c>
       <c r="G14">
-        <v>-0.8224730844448677</v>
+        <v>-2.96837532409153</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-7.578782690430646</v>
       </c>
       <c r="E15">
-        <v>-17.30645760639938</v>
+        <v>-18.76498398631584</v>
       </c>
       <c r="F15">
-        <v>3.78253996109236</v>
+        <v>3.854288175318436</v>
       </c>
       <c r="G15">
-        <v>-2.224942665065095</v>
+        <v>-3.371017114759848</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-7.717150404520708</v>
       </c>
       <c r="E16">
-        <v>-16.95132108929585</v>
+        <v>-18.77694821464411</v>
       </c>
       <c r="F16">
-        <v>4.293632708210821</v>
+        <v>4.727036190090328</v>
       </c>
       <c r="G16">
-        <v>0.2061796255174756</v>
+        <v>-2.583547578970029</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-7.793303016316439</v>
       </c>
       <c r="E17">
-        <v>-17.15508430574499</v>
+        <v>-20.01375597867102</v>
       </c>
       <c r="F17">
-        <v>5.258488551234796</v>
+        <v>4.79086189847603</v>
       </c>
       <c r="G17">
-        <v>-1.019626002945085</v>
+        <v>-3.041104699043778</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-7.809924921611071</v>
       </c>
       <c r="E18">
-        <v>-19.86594205858665</v>
+        <v>-21.40880220994796</v>
       </c>
       <c r="F18">
-        <v>5.279434649381984</v>
+        <v>5.367852929221998</v>
       </c>
       <c r="G18">
-        <v>-1.072118013015769</v>
+        <v>-2.247782118740528</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-7.768241146365717</v>
       </c>
       <c r="E19">
-        <v>-21.22646773250312</v>
+        <v>-21.1497644397612</v>
       </c>
       <c r="F19">
-        <v>4.88156647234777</v>
+        <v>5.108598783167836</v>
       </c>
       <c r="G19">
-        <v>-0.03198433112323285</v>
+        <v>-2.797484963354351</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-7.670114208113065</v>
       </c>
       <c r="E20">
-        <v>-20.63935107740866</v>
+        <v>-22.8660153324022</v>
       </c>
       <c r="F20">
-        <v>5.261815274724439</v>
+        <v>5.999652060806792</v>
       </c>
       <c r="G20">
-        <v>-0.4719425911102165</v>
+        <v>-2.660795848583383</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-7.514039819577617</v>
       </c>
       <c r="E21">
-        <v>-22.40632087893556</v>
+        <v>-22.42551708025408</v>
       </c>
       <c r="F21">
-        <v>5.799612930174351</v>
+        <v>6.115423032287246</v>
       </c>
       <c r="G21">
-        <v>0.6496073372296155</v>
+        <v>-1.761535811023454</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-7.311232113225514</v>
       </c>
       <c r="E22">
-        <v>-20.42225603348094</v>
+        <v>-23.56032549573223</v>
       </c>
       <c r="F22">
-        <v>5.402346147874569</v>
+        <v>6.283134296658033</v>
       </c>
       <c r="G22">
-        <v>1.675767206400887</v>
+        <v>-1.417748898952298</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-7.071125715528879</v>
       </c>
       <c r="E23">
-        <v>-22.9065180039268</v>
+        <v>-23.96784287168248</v>
       </c>
       <c r="F23">
-        <v>5.708245662380371</v>
+        <v>6.852835694259365</v>
       </c>
       <c r="G23">
-        <v>2.698874752584952</v>
+        <v>-1.968679955961191</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-6.803623384943742</v>
       </c>
       <c r="E24">
-        <v>-22.66275930504192</v>
+        <v>-25.49363067603487</v>
       </c>
       <c r="F24">
-        <v>6.008323410779298</v>
+        <v>6.664879130564158</v>
       </c>
       <c r="G24">
-        <v>1.357792617899429</v>
+        <v>-1.523328817290735</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-6.51385467288583</v>
       </c>
       <c r="E25">
-        <v>-23.15196129514253</v>
+        <v>-24.63323419999952</v>
       </c>
       <c r="F25">
-        <v>6.681540912504067</v>
+        <v>7.028520823249501</v>
       </c>
       <c r="G25">
-        <v>-0.05783307069386228</v>
+        <v>-0.8130612034767196</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-6.217153228921943</v>
       </c>
       <c r="E26">
-        <v>-21.85012011589147</v>
+        <v>-24.96443320349851</v>
       </c>
       <c r="F26">
-        <v>6.708497644525968</v>
+        <v>6.9956760557285</v>
       </c>
       <c r="G26">
-        <v>0.9140504043610587</v>
+        <v>-1.501621570189734</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-5.924376354499774</v>
       </c>
       <c r="E27">
-        <v>-23.71390869170236</v>
+        <v>-25.98036917627531</v>
       </c>
       <c r="F27">
-        <v>6.451135489619801</v>
+        <v>6.952314335661558</v>
       </c>
       <c r="G27">
-        <v>1.849008054470949</v>
+        <v>-1.032292150178336</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-5.642629984024581</v>
       </c>
       <c r="E28">
-        <v>-24.19181213915384</v>
+        <v>-26.34807220875013</v>
       </c>
       <c r="F28">
-        <v>6.621234108845457</v>
+        <v>6.565622491625915</v>
       </c>
       <c r="G28">
-        <v>0.5958010405798408</v>
+        <v>-1.27097586246871</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-5.372592609328897</v>
       </c>
       <c r="E29">
-        <v>-24.57218131342811</v>
+        <v>-25.29292417954091</v>
       </c>
       <c r="F29">
-        <v>5.541962503412009</v>
+        <v>6.89646414863001</v>
       </c>
       <c r="G29">
-        <v>1.488661793612359</v>
+        <v>-1.509447699844571</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-5.12311388753388</v>
       </c>
       <c r="E30">
-        <v>-23.62845185870362</v>
+        <v>-25.97952235163588</v>
       </c>
       <c r="F30">
-        <v>6.872257596385403</v>
+        <v>6.851059674547763</v>
       </c>
       <c r="G30">
-        <v>1.103241460839328</v>
+        <v>-0.8739619992171523</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-4.899298837817264</v>
       </c>
       <c r="E31">
-        <v>-24.17948110443096</v>
+        <v>-25.87428061569761</v>
       </c>
       <c r="F31">
-        <v>6.283366239530817</v>
+        <v>6.699317676968144</v>
       </c>
       <c r="G31">
-        <v>1.177940610387443</v>
+        <v>-1.678570229263779</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-4.703829359457979</v>
       </c>
       <c r="E32">
-        <v>-24.67638602881862</v>
+        <v>-26.01406555136639</v>
       </c>
       <c r="F32">
-        <v>6.27608489006021</v>
+        <v>6.633974399500513</v>
       </c>
       <c r="G32">
-        <v>1.700169237570855</v>
+        <v>-1.428902126874103</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-4.535172105755425</v>
       </c>
       <c r="E33">
-        <v>-24.8733293634122</v>
+        <v>-26.27145042854034</v>
       </c>
       <c r="F33">
-        <v>6.227863966808444</v>
+        <v>6.231520380524402</v>
       </c>
       <c r="G33">
-        <v>0.3815690176425238</v>
+        <v>-1.643236776723138</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-4.400350878104172</v>
       </c>
       <c r="E34">
-        <v>-22.87637648093175</v>
+        <v>-25.07179426527236</v>
       </c>
       <c r="F34">
-        <v>5.639338748345897</v>
+        <v>5.949052066374187</v>
       </c>
       <c r="G34">
-        <v>2.019908346844745</v>
+        <v>-1.449761874317051</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-4.304065535864908</v>
       </c>
       <c r="E35">
-        <v>-24.37239409715771</v>
+        <v>-24.27341071229805</v>
       </c>
       <c r="F35">
-        <v>5.315925890210108</v>
+        <v>6.156978911416085</v>
       </c>
       <c r="G35">
-        <v>1.108068236235586</v>
+        <v>-0.8127036645584783</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-4.247912235707267</v>
       </c>
       <c r="E36">
-        <v>-21.83619052984387</v>
+        <v>-24.6964471686726</v>
       </c>
       <c r="F36">
-        <v>5.694315836134894</v>
+        <v>6.258710712153893</v>
       </c>
       <c r="G36">
-        <v>1.025258250116256</v>
+        <v>-1.397306280247299</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-4.227318991728848</v>
       </c>
       <c r="E37">
-        <v>-23.08146654026513</v>
+        <v>-24.546731289505</v>
       </c>
       <c r="F37">
-        <v>5.261189028967922</v>
+        <v>6.024080615515349</v>
       </c>
       <c r="G37">
-        <v>0.6124365319146786</v>
+        <v>-0.6072081712992979</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-4.24227391459157</v>
       </c>
       <c r="E38">
-        <v>-23.14795359564575</v>
+        <v>-24.97621629286647</v>
       </c>
       <c r="F38">
-        <v>5.693439423422732</v>
+        <v>5.796294490358735</v>
       </c>
       <c r="G38">
-        <v>1.160613215034898</v>
+        <v>-1.054211272193851</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-4.290629176909336</v>
       </c>
       <c r="E39">
-        <v>-22.33530082107327</v>
+        <v>-24.38282317279738</v>
       </c>
       <c r="F39">
-        <v>5.160751138113288</v>
+        <v>5.75900967355873</v>
       </c>
       <c r="G39">
-        <v>1.35737879970702</v>
+        <v>-1.102141350511419</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.366736859062075</v>
       </c>
       <c r="E40">
-        <v>-22.24909678986326</v>
+        <v>-23.81855719754562</v>
       </c>
       <c r="F40">
-        <v>5.689557693773214</v>
+        <v>5.606354815101226</v>
       </c>
       <c r="G40">
-        <v>1.942252880130061</v>
+        <v>-1.343125891951586</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.460343388077251</v>
       </c>
       <c r="E41">
-        <v>-20.86668047259371</v>
+        <v>-22.74078491219408</v>
       </c>
       <c r="F41">
-        <v>5.318122720562332</v>
+        <v>5.517002136830855</v>
       </c>
       <c r="G41">
-        <v>0.969429210141987</v>
+        <v>-1.218470610215869</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.566411195047018</v>
       </c>
       <c r="E42">
-        <v>-21.04891079513638</v>
+        <v>-23.79921608505886</v>
       </c>
       <c r="F42">
-        <v>5.023382971707046</v>
+        <v>5.413184506972798</v>
       </c>
       <c r="G42">
-        <v>1.449815852254551</v>
+        <v>-1.496678925699602</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-4.681319339629936</v>
       </c>
       <c r="E43">
-        <v>-20.87065647277245</v>
+        <v>-23.2039527052246</v>
       </c>
       <c r="F43">
-        <v>5.531379281473843</v>
+        <v>5.55369218583565</v>
       </c>
       <c r="G43">
-        <v>1.961977110453039</v>
+        <v>-0.949144488414001</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.800506124667273</v>
       </c>
       <c r="E44">
-        <v>-20.79470943518981</v>
+        <v>-21.61064988189185</v>
       </c>
       <c r="F44">
-        <v>4.993931197067912</v>
+        <v>5.650203615201015</v>
       </c>
       <c r="G44">
-        <v>0.9026091589773374</v>
+        <v>-0.7485552236440206</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-4.917225674955639</v>
       </c>
       <c r="E45">
-        <v>-18.59949090370553</v>
+        <v>-21.58752296513468</v>
       </c>
       <c r="F45">
-        <v>5.389991876429217</v>
+        <v>5.607658665393232</v>
       </c>
       <c r="G45">
-        <v>0.9091143809620053</v>
+        <v>-0.4784709869136593</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-5.030385167722678</v>
       </c>
       <c r="E46">
-        <v>-18.12217615787505</v>
+        <v>-22.05543207045123</v>
       </c>
       <c r="F46">
-        <v>5.463834203449571</v>
+        <v>5.424576215496097</v>
       </c>
       <c r="G46">
-        <v>2.184339833234806</v>
+        <v>-0.3086896589321365</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-5.142558029922926</v>
       </c>
       <c r="E47">
-        <v>-18.28913646606385</v>
+        <v>-21.24842630296632</v>
       </c>
       <c r="F47">
-        <v>5.273599629396664</v>
+        <v>5.550009264362804</v>
       </c>
       <c r="G47">
-        <v>2.204653340663774</v>
+        <v>-0.7016911409900977</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-5.25493108298381</v>
       </c>
       <c r="E48">
-        <v>-18.47547411453147</v>
+        <v>-20.9086503696968</v>
       </c>
       <c r="F48">
-        <v>5.081062193963976</v>
+        <v>5.774861312178701</v>
       </c>
       <c r="G48">
-        <v>1.727031004076502</v>
+        <v>0.04176469185511138</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-5.365777576630835</v>
       </c>
       <c r="E49">
-        <v>-18.1214380166118</v>
+        <v>-20.65483393004088</v>
       </c>
       <c r="F49">
-        <v>5.395754000083091</v>
+        <v>5.906132694500339</v>
       </c>
       <c r="G49">
-        <v>0.9510424402168749</v>
+        <v>-0.466162378598649</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-5.47656742932238</v>
       </c>
       <c r="E50">
-        <v>-14.92595203241727</v>
+        <v>-19.14002314668309</v>
       </c>
       <c r="F50">
-        <v>5.3823526722406</v>
+        <v>5.468461463761609</v>
       </c>
       <c r="G50">
-        <v>1.726802576434292</v>
+        <v>-0.08127835420298082</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-5.592939448572497</v>
       </c>
       <c r="E51">
-        <v>-17.15611226934473</v>
+        <v>-18.76101251461112</v>
       </c>
       <c r="F51">
-        <v>4.957857453410799</v>
+        <v>5.450144603750906</v>
       </c>
       <c r="G51">
-        <v>2.433647086160701</v>
+        <v>-0.09310031232371824</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-5.717011206221775</v>
       </c>
       <c r="E52">
-        <v>-15.7939563447855</v>
+        <v>-19.9276606308372</v>
       </c>
       <c r="F52">
-        <v>5.343555256563083</v>
+        <v>5.388176095082281</v>
       </c>
       <c r="G52">
-        <v>1.566075590502676</v>
+        <v>0.1256009470916149</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-5.84685485342933</v>
       </c>
       <c r="E53">
-        <v>-16.813845675371</v>
+        <v>-18.10374526866384</v>
       </c>
       <c r="F53">
-        <v>5.656938242185775</v>
+        <v>5.232514262952614</v>
       </c>
       <c r="G53">
-        <v>1.740273186233587</v>
+        <v>0.245687675983138</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-5.982460038266183</v>
       </c>
       <c r="E54">
-        <v>-16.92946667373483</v>
+        <v>-18.13079837238566</v>
       </c>
       <c r="F54">
-        <v>5.428169673289441</v>
+        <v>5.534503883317202</v>
       </c>
       <c r="G54">
-        <v>-0.1461120780440678</v>
+        <v>0.1805162764970454</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-6.128360238954428</v>
       </c>
       <c r="E55">
-        <v>-15.81910296095009</v>
+        <v>-17.80046883589614</v>
       </c>
       <c r="F55">
-        <v>5.203123787501288</v>
+        <v>5.351552315469709</v>
       </c>
       <c r="G55">
-        <v>1.080312622434336</v>
+        <v>-0.5627210603425717</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-6.284849026843538</v>
       </c>
       <c r="E56">
-        <v>-16.73371432780527</v>
+        <v>-18.84741127020346</v>
       </c>
       <c r="F56">
-        <v>5.057915951994952</v>
+        <v>5.238203490275041</v>
       </c>
       <c r="G56">
-        <v>1.559567057972469</v>
+        <v>0.1556971165891293</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-6.447779959557861</v>
       </c>
       <c r="E57">
-        <v>-13.88811183086537</v>
+        <v>-17.13996373103338</v>
       </c>
       <c r="F57">
-        <v>5.675823362234798</v>
+        <v>5.673356484109261</v>
       </c>
       <c r="G57">
-        <v>1.118734813963118</v>
+        <v>-0.2406678797367314</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-6.614037150978065</v>
       </c>
       <c r="E58">
-        <v>-13.32884981939209</v>
+        <v>-16.24587993685497</v>
       </c>
       <c r="F58">
-        <v>5.667110593892152</v>
+        <v>5.439375827514513</v>
       </c>
       <c r="G58">
-        <v>0.9694987315983118</v>
+        <v>-0.4384663546171063</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-6.786617959790666</v>
       </c>
       <c r="E59">
-        <v>-14.16783567031917</v>
+        <v>-16.03013890665555</v>
       </c>
       <c r="F59">
-        <v>5.314729727680466</v>
+        <v>5.509366246111848</v>
       </c>
       <c r="G59">
-        <v>1.648584316977932</v>
+        <v>0.2437973544802141</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-6.96429460522971</v>
       </c>
       <c r="E60">
-        <v>-12.81913384203673</v>
+        <v>-17.13036336613711</v>
       </c>
       <c r="F60">
-        <v>5.295993713763946</v>
+        <v>5.63793715070036</v>
       </c>
       <c r="G60">
-        <v>0.5991446915745048</v>
+        <v>0.01626355956610543</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-7.141678797527896</v>
       </c>
       <c r="E61">
-        <v>-12.19739700315363</v>
+        <v>-15.59373892348437</v>
       </c>
       <c r="F61">
-        <v>5.308720750540558</v>
+        <v>5.394488254691614</v>
       </c>
       <c r="G61">
-        <v>0.6255562238868103</v>
+        <v>-0.5766981836093747</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-7.314184877548906</v>
       </c>
       <c r="E62">
-        <v>-12.06055557558984</v>
+        <v>-15.63793230132523</v>
       </c>
       <c r="F62">
-        <v>5.372213455230335</v>
+        <v>5.363707778738389</v>
       </c>
       <c r="G62">
-        <v>0.6888008858690471</v>
+        <v>-0.7842726994672174</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-7.4842451317474</v>
       </c>
       <c r="E63">
-        <v>-12.85020823067736</v>
+        <v>-15.06574149656005</v>
       </c>
       <c r="F63">
-        <v>5.212008856263716</v>
+        <v>5.805948284070961</v>
       </c>
       <c r="G63">
-        <v>-0.5053228217826879</v>
+        <v>-0.3564508994272019</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-7.649219472465451</v>
       </c>
       <c r="E64">
-        <v>-12.04385003497555</v>
+        <v>-16.20319001238466</v>
       </c>
       <c r="F64">
-        <v>4.810328532441819</v>
+        <v>5.685046404897568</v>
       </c>
       <c r="G64">
-        <v>-0.1924133679563146</v>
+        <v>-0.9574506471720324</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-7.802963478840617</v>
       </c>
       <c r="E65">
-        <v>-12.76015046808682</v>
+        <v>-16.01277220883613</v>
       </c>
       <c r="F65">
-        <v>5.414513208286889</v>
+        <v>5.608405852790558</v>
       </c>
       <c r="G65">
-        <v>0.006557040044962307</v>
+        <v>-0.7373225426292734</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-7.939532155801344</v>
       </c>
       <c r="E66">
-        <v>-12.2305046766237</v>
+        <v>-15.41570649634682</v>
       </c>
       <c r="F66">
-        <v>5.001234084090993</v>
+        <v>5.461483296760426</v>
       </c>
       <c r="G66">
-        <v>-0.1319462536815263</v>
+        <v>-0.8714095686063743</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-8.061306483842827</v>
       </c>
       <c r="E67">
-        <v>-12.67985156698281</v>
+        <v>-15.57032218439071</v>
       </c>
       <c r="F67">
-        <v>4.951202349696708</v>
+        <v>5.613720658046919</v>
       </c>
       <c r="G67">
-        <v>-0.3614663759191977</v>
+        <v>-1.183474833320233</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-8.165281672443722</v>
       </c>
       <c r="E68">
-        <v>-11.93585951531463</v>
+        <v>-14.43490695339553</v>
       </c>
       <c r="F68">
-        <v>4.914760810912752</v>
+        <v>5.306267126293466</v>
       </c>
       <c r="G68">
-        <v>0.3114251787564459</v>
+        <v>-0.679050320047022</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-8.245422971582316</v>
       </c>
       <c r="E69">
-        <v>-13.07761008144654</v>
+        <v>-14.74324169162979</v>
       </c>
       <c r="F69">
-        <v>4.773497660978547</v>
+        <v>5.130716192822583</v>
       </c>
       <c r="G69">
-        <v>0.2220040331951919</v>
+        <v>-1.225015558747008</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-8.295734065064092</v>
       </c>
       <c r="E70">
-        <v>-11.5689127379991</v>
+        <v>-14.33849574177223</v>
       </c>
       <c r="F70">
-        <v>4.915436758713437</v>
+        <v>5.564896683325916</v>
       </c>
       <c r="G70">
-        <v>0.9300602025889741</v>
+        <v>-1.525553503893125</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-8.319495715245255</v>
       </c>
       <c r="E71">
-        <v>-12.27464371277647</v>
+        <v>-14.98767966161582</v>
       </c>
       <c r="F71">
-        <v>5.621547073268569</v>
+        <v>5.107964253737292</v>
       </c>
       <c r="G71">
-        <v>-0.7014527817112701</v>
+        <v>-1.508130102719941</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-8.314779934300379</v>
       </c>
       <c r="E72">
-        <v>-11.60625000619234</v>
+        <v>-14.64419037966002</v>
       </c>
       <c r="F72">
-        <v>5.099614310317073</v>
+        <v>5.094307788734739</v>
       </c>
       <c r="G72">
-        <v>-0.3523822389594376</v>
+        <v>-1.233897752428873</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-8.277738444708547</v>
       </c>
       <c r="E73">
-        <v>-12.84657639452321</v>
+        <v>-14.7597162800697</v>
       </c>
       <c r="F73">
-        <v>5.011924993791523</v>
+        <v>5.038349913940827</v>
       </c>
       <c r="G73">
-        <v>0.7971020726407647</v>
+        <v>-1.354087108232113</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-8.205103008926107</v>
       </c>
       <c r="E74">
-        <v>-13.12785350056164</v>
+        <v>-14.64653612919599</v>
       </c>
       <c r="F74">
-        <v>4.71376574429748</v>
+        <v>5.291878384506838</v>
       </c>
       <c r="G74">
-        <v>-0.4601272540805577</v>
+        <v>-0.4825826844734341</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-8.104002727243381</v>
       </c>
       <c r="E75">
-        <v>-13.58197793099884</v>
+        <v>-14.81626786347748</v>
       </c>
       <c r="F75">
-        <v>4.615243038878118</v>
+        <v>5.135252332720313</v>
       </c>
       <c r="G75">
-        <v>-0.2961393807927594</v>
+        <v>-0.9055975723904278</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-7.976688368813409</v>
       </c>
       <c r="E76">
-        <v>-12.40559359565627</v>
+        <v>-15.28371959291926</v>
       </c>
       <c r="F76">
-        <v>4.033374580864467</v>
+        <v>4.849969226135386</v>
       </c>
       <c r="G76">
-        <v>0.4847785853748424</v>
+        <v>-0.7298804362569918</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-7.824333284167502</v>
       </c>
       <c r="E77">
-        <v>-12.36848275116341</v>
+        <v>-15.72726097960053</v>
       </c>
       <c r="F77">
-        <v>4.629466107184186</v>
+        <v>4.612277483576096</v>
       </c>
       <c r="G77">
-        <v>0.5409022639021068</v>
+        <v>-0.8483152029244185</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-7.648312072336231</v>
       </c>
       <c r="E78">
-        <v>-13.01550658890534</v>
+        <v>-16.22140353484351</v>
       </c>
       <c r="F78">
-        <v>4.1820433353797</v>
+        <v>4.63433193730823</v>
       </c>
       <c r="G78">
-        <v>0.2042628196502376</v>
+        <v>-0.6097705335466939</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-7.460418783906985</v>
       </c>
       <c r="E79">
-        <v>-12.8589708278822</v>
+        <v>-16.88039160091371</v>
       </c>
       <c r="F79">
-        <v>4.288364291529017</v>
+        <v>4.5003998388888</v>
       </c>
       <c r="G79">
-        <v>0.5932320572413664</v>
+        <v>-1.031130148694052</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-7.266645373214058</v>
       </c>
       <c r="E80">
-        <v>-15.84978790082607</v>
+        <v>-16.29000538758571</v>
       </c>
       <c r="F80">
-        <v>4.355549858100473</v>
+        <v>4.778870451953105</v>
       </c>
       <c r="G80">
-        <v>1.663591019907448</v>
+        <v>-0.468810815030066</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-7.070507312016755</v>
       </c>
       <c r="E81">
-        <v>-15.39470796237325</v>
+        <v>-17.52863812663772</v>
       </c>
       <c r="F81">
-        <v>4.353800346145761</v>
+        <v>4.55438619926405</v>
       </c>
       <c r="G81">
-        <v>0.6701889988472645</v>
+        <v>-0.06134224896548974</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-6.87361611339726</v>
       </c>
       <c r="E82">
-        <v>-16.61652194896077</v>
+        <v>-18.8851017593693</v>
       </c>
       <c r="F82">
-        <v>4.13459610728215</v>
+        <v>4.468814189820055</v>
       </c>
       <c r="G82">
-        <v>1.086672180415276</v>
+        <v>0.3355193291912616</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-6.686238752140579</v>
       </c>
       <c r="E83">
-        <v>-16.46446937720522</v>
+        <v>-18.63005810325731</v>
       </c>
       <c r="F83">
-        <v>3.840643307459523</v>
+        <v>4.12736445985571</v>
       </c>
       <c r="G83">
-        <v>2.404421590140015</v>
+        <v>0.8757904295637016</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-6.510779983803822</v>
       </c>
       <c r="E84">
-        <v>-15.81396314295139</v>
+        <v>-18.36374307534022</v>
       </c>
       <c r="F84">
-        <v>3.419898936229598</v>
+        <v>4.312128495580529</v>
       </c>
       <c r="G84">
-        <v>1.96664829020895</v>
+        <v>0.4650940815983359</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-6.34640892302504</v>
       </c>
       <c r="E85">
-        <v>-15.04165001483924</v>
+        <v>-19.61463439353099</v>
       </c>
       <c r="F85">
-        <v>4.330185248226752</v>
+        <v>4.058560263379183</v>
       </c>
       <c r="G85">
-        <v>2.068103268805455</v>
+        <v>0.1119548783787391</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-6.189209522848495</v>
       </c>
       <c r="E86">
-        <v>-17.95933223255923</v>
+        <v>-20.98006893327177</v>
       </c>
       <c r="F86">
-        <v>3.404918740117372</v>
+        <v>3.610607336436906</v>
       </c>
       <c r="G86">
-        <v>2.478998249503177</v>
+        <v>0.8075004961796155</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-6.044582344113743</v>
       </c>
       <c r="E87">
-        <v>-18.71573683148243</v>
+        <v>-22.20156592667875</v>
       </c>
       <c r="F87">
-        <v>3.086684834983886</v>
+        <v>3.916468746042178</v>
       </c>
       <c r="G87">
-        <v>2.117576061344324</v>
+        <v>0.7670224558709466</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-5.910639762562186</v>
       </c>
       <c r="E88">
-        <v>-19.57185842805453</v>
+        <v>-23.15202922225265</v>
       </c>
       <c r="F88">
-        <v>3.403855116372177</v>
+        <v>3.599740812846982</v>
       </c>
       <c r="G88">
-        <v>2.307257078562406</v>
+        <v>0.6965839784318736</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-5.783557170835929</v>
       </c>
       <c r="E89">
-        <v>-21.22680283957969</v>
+        <v>-23.86715678059594</v>
       </c>
       <c r="F89">
-        <v>3.402385592599611</v>
+        <v>3.665191778076976</v>
       </c>
       <c r="G89">
-        <v>3.021066976103441</v>
+        <v>1.614436039740349</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-5.656913585015588</v>
       </c>
       <c r="E90">
-        <v>-22.13094437452913</v>
+        <v>-25.26448989124675</v>
       </c>
       <c r="F90">
-        <v>3.23849641542534</v>
+        <v>3.115049791590546</v>
       </c>
       <c r="G90">
-        <v>1.478041563522377</v>
+        <v>0.9139974356324303</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-5.53534173616924</v>
       </c>
       <c r="E91">
-        <v>-27.34122995726834</v>
+        <v>-26.4179012779484</v>
       </c>
       <c r="F91">
-        <v>3.217966157714357</v>
+        <v>3.128547210051762</v>
       </c>
       <c r="G91">
-        <v>1.557852195383126</v>
+        <v>0.7793939645512031</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-5.41782167356373</v>
       </c>
       <c r="E92">
-        <v>-26.49610802406087</v>
+        <v>-27.76143611738809</v>
       </c>
       <c r="F92">
-        <v>2.934189023067719</v>
+        <v>3.103906593288087</v>
       </c>
       <c r="G92">
-        <v>1.303079231771894</v>
+        <v>1.428585323711204</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-5.303197664871985</v>
       </c>
       <c r="E93">
-        <v>-28.56784412630399</v>
+        <v>-30.62986665180066</v>
       </c>
       <c r="F93">
-        <v>3.659881943025032</v>
+        <v>2.923600830925136</v>
       </c>
       <c r="G93">
-        <v>1.359322089938573</v>
+        <v>1.474793918348352</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-5.187728046604102</v>
       </c>
       <c r="E94">
-        <v>-32.27601223832891</v>
+        <v>-31.13135665612108</v>
       </c>
       <c r="F94">
-        <v>2.372017485157834</v>
+        <v>2.985087229765332</v>
       </c>
       <c r="G94">
-        <v>1.420116948221749</v>
+        <v>1.843697939425958</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-5.07840131924852</v>
       </c>
       <c r="E95">
-        <v>-32.06579141794484</v>
+        <v>-33.18667024737539</v>
       </c>
       <c r="F95">
-        <v>2.64248441237629</v>
+        <v>2.327514274809834</v>
       </c>
       <c r="G95">
-        <v>2.726706508933604</v>
+        <v>1.318966539814857</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-4.975205395497756</v>
       </c>
       <c r="E96">
-        <v>-33.72070186591493</v>
+        <v>-34.76499287869076</v>
       </c>
       <c r="F96">
-        <v>1.57523738816188</v>
+        <v>2.356059815510305</v>
       </c>
       <c r="G96">
-        <v>2.330295164970194</v>
+        <v>0.6296215738090354</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-4.878158043892578</v>
       </c>
       <c r="E97">
-        <v>-35.17421748934191</v>
+        <v>-36.73638705387192</v>
       </c>
       <c r="F97">
-        <v>2.05789393907704</v>
+        <v>1.996180567568477</v>
       </c>
       <c r="G97">
-        <v>1.23727882863334</v>
+        <v>0.9906233226844012</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.780575833031572</v>
       </c>
       <c r="E98">
-        <v>-37.63915193272303</v>
+        <v>-38.21891887450304</v>
       </c>
       <c r="F98">
-        <v>2.020105474896132</v>
+        <v>1.700166789647684</v>
       </c>
       <c r="G98">
-        <v>1.925299576423453</v>
+        <v>1.227602104022051</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.688798148656515</v>
       </c>
       <c r="E99">
-        <v>-40.02702986238963</v>
+        <v>-41.58028739007255</v>
       </c>
       <c r="F99">
-        <v>1.258618799463853</v>
+        <v>1.052409988415361</v>
       </c>
       <c r="G99">
-        <v>0.4475018426026488</v>
+        <v>0.3202444720730644</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.596653837189822</v>
       </c>
       <c r="E100">
-        <v>-41.52542719170663</v>
+        <v>-43.19516386357783</v>
       </c>
       <c r="F100">
-        <v>1.348084135701005</v>
+        <v>1.156327022361753</v>
       </c>
       <c r="G100">
-        <v>1.743067286668732</v>
+        <v>0.6114466787984365</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.506444976274837</v>
       </c>
       <c r="E101">
-        <v>-44.08779401759978</v>
+        <v>-44.48644916991702</v>
       </c>
       <c r="F101">
-        <v>1.370781402537711</v>
+        <v>0.9990018284872653</v>
       </c>
       <c r="G101">
-        <v>0.8543645788335384</v>
+        <v>-0.1389017098595351</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.400515009568335</v>
       </c>
       <c r="E102">
-        <v>-47.02821596754929</v>
+        <v>-46.3119698761261</v>
       </c>
       <c r="F102">
-        <v>0.7166610829170817</v>
+        <v>0.5627959796840876</v>
       </c>
       <c r="G102">
-        <v>0.9370818696777683</v>
+        <v>0.1104088536118994</v>
       </c>
     </row>
   </sheetData>
